--- a/data/trees/robustness_analyses.xlsx
+++ b/data/trees/robustness_analyses.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Eukaryotes_Asgard_TACK/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Asgard_Eukaryote_Data/data/trees/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6CB6B1F-A8F0-9B49-ADAF-FCC8E14B28CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19C4C65-FEE3-494E-BF8F-5EAD292AB805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="720" windowWidth="28040" windowHeight="17340" xr2:uid="{A8F32809-49F2-F649-AE47-172A25B57BE0}"/>
   </bookViews>
@@ -424,6 +424,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -449,12 +455,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -828,7 +828,7 @@
       <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="15" t="s">
         <v>39</v>
       </c>
     </row>
@@ -879,13 +879,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="17">
         <v>4740</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="17" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -902,9 +902,9 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="8" t="s">
         <v>16</v>
       </c>
@@ -919,9 +919,9 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
       <c r="D7" s="5" t="s">
         <v>18</v>
       </c>
@@ -931,14 +931,14 @@
       <c r="F7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="16">
         <v>6.3600000000000001E-5</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
       <c r="D8" s="8" t="s">
         <v>20</v>
       </c>
@@ -953,9 +953,9 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
       <c r="D9" s="5" t="s">
         <v>22</v>
       </c>
@@ -993,16 +993,16 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="17">
         <v>4740</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="10">
@@ -1016,10 +1016,10 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
       <c r="E12" s="11">
         <v>11443</v>
       </c>
@@ -1031,10 +1031,10 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
       <c r="E13" s="10">
         <v>10636</v>
       </c>
@@ -1046,10 +1046,10 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="19"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
       <c r="E14" s="11">
         <v>12675</v>
       </c>
@@ -1061,10 +1061,10 @@
       </c>
     </row>
     <row r="15" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
       <c r="E15" s="10">
         <v>11350</v>
       </c>
@@ -1076,10 +1076,10 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
       <c r="E16" s="11">
         <v>11016</v>
       </c>
@@ -1091,10 +1091,10 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="19"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
       <c r="E17" s="10">
         <v>10894</v>
       </c>
@@ -1106,10 +1106,10 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
       <c r="E18" s="11">
         <v>10078</v>
       </c>
@@ -1121,10 +1121,10 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
       <c r="E19" s="10">
         <v>10096</v>
       </c>
@@ -1136,10 +1136,10 @@
       </c>
     </row>
     <row r="20" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
       <c r="E20" s="12">
         <v>10861</v>
       </c>

--- a/data/trees/robustness_analyses.xlsx
+++ b/data/trees/robustness_analyses.xlsx
@@ -1,48 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Asgard_Eukaryote_Data/data/trees/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Nature_submission_rechecked_precise_red/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19C4C65-FEE3-494E-BF8F-5EAD292AB805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5961AB62-CAF6-184E-9C9B-988589E1AB64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="720" windowWidth="28040" windowHeight="17340" xr2:uid="{A8F32809-49F2-F649-AE47-172A25B57BE0}"/>
+    <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
-  <si>
-    <t>Extended Data Table 5 | Independent robustness analyses supporting the consensus placement of eukaryotes outside extant Asgard diversity</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="40">
   <si>
     <t>Robustness analysis</t>
   </si>
@@ -59,7 +37,7 @@
     <t>Chain length</t>
   </si>
   <si>
-    <t>Eukaryotic placement</t>
+    <t>AU P value</t>
   </si>
   <si>
     <t>Independently curated ultra-clean dataset</t>
@@ -80,59 +58,21 @@
     <t>(TACK, Asgard) → Euk [100/100]</t>
   </si>
   <si>
-    <t>Topology test (AU-test)</t>
-  </si>
-  <si>
     <t>(TACK, Asgard) → Euk</t>
   </si>
   <si>
-    <t>(TACK, Asgard) → Euk: P-value=0.999</t>
-  </si>
-  <si>
     <t>Hod → Euk</t>
   </si>
   <si>
-    <r>
-      <t>Hod → Euk: P-value=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>0.000255</t>
-    </r>
-  </si>
-  <si>
     <t>Heimdall → Euk</t>
   </si>
   <si>
-    <t>Heimdall → Euk: P-value=6.36e-05</t>
-  </si>
-  <si>
     <t>Njord → Euk</t>
   </si>
   <si>
-    <t>Njord → Euk: P-value=0.000263</t>
-  </si>
-  <si>
     <t>TACK → Euk</t>
   </si>
   <si>
-    <t>TACK → Euk: P-value=0.00158</t>
-  </si>
-  <si>
     <t>Alternative phylogenetic model (PMSF)</t>
   </si>
   <si>
@@ -142,9 +82,6 @@
     <t>(TACK, Asgard) → Euk [74/94]</t>
   </si>
   <si>
-    <t>CAT+GTR</t>
-  </si>
-  <si>
     <t>(Hod + Wukong, Euk) → Other Asgard [0.81/0.96]</t>
   </si>
   <si>
@@ -172,26 +109,48 @@
     <t>(TACK, Asgard) → Euk [0.65/0.97]</t>
   </si>
   <si>
-    <t>CAT-GTR chain-level sensitivity analysis (10 independent chains; default burnin = 1/10 of the chain; default sampling frequency=1; non-converged)</t>
-  </si>
-  <si>
     <t>For CAT-GTR analyses, all chains used the same burn-in and sampling settings. Because convergence diagnostics consistently indicated non-convergence, chain-level topologies are summarized descriptively and are not interpreted as posterior consensus support.</t>
   </si>
   <si>
-    <t>AU P value</t>
+    <t>AU topology tests</t>
+  </si>
+  <si>
+    <t>P = 0.999</t>
+  </si>
+  <si>
+    <t>P = 2.55 × 10⁻⁴</t>
+  </si>
+  <si>
+    <t>P = 6.36 × 10⁻⁵</t>
+  </si>
+  <si>
+    <t>P = 2.63 × 10⁻⁴</t>
+  </si>
+  <si>
+    <t>P = 1.58 × 10⁻³</t>
+  </si>
+  <si>
+    <t>CAT-GTR chain-level sensitivity analysis (10 independent, non-converged chains)</t>
+  </si>
+  <si>
+    <t>CAT-GTR</t>
+  </si>
+  <si>
+    <t>Eukaryote placement</t>
+  </si>
+  <si>
+    <t>Extended Data Table 5 | Independent tests of the TACK–Asgard topology</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -208,19 +167,19 @@
     </font>
     <font>
       <b/>
-      <sz val="10.5"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -229,6 +188,13 @@
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -243,13 +209,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCCCCC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -386,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -423,11 +387,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -439,7 +420,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -448,13 +429,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -475,7 +465,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -517,108 +507,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -626,80 +522,31 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -729,22 +576,22 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -759,404 +606,404 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9489FE61-F365-4949-B9AF-80541731C9BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28" style="1" customWidth="1"/>
+    <col min="1" max="1" width="59.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.1640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" style="1"/>
     <col min="6" max="6" width="37.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" customWidth="1"/>
     <col min="8" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="47" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="G2" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="32" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="B3" s="5">
         <v>4743</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="B4" s="8">
         <v>4787</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="30">
+        <v>4740</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="E5" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="28"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="17">
-        <v>4740</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="E6" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="28"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="E7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="28"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="6">
-        <v>0.999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="8" t="s">
+      <c r="E8" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="29"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="E9" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="G6" s="9">
-        <v>2.5500000000000002E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="16">
-        <v>6.3600000000000001E-5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="9">
-        <v>2.63E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="6">
-        <v>1.58E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="31" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="B10" s="8">
         <v>4740</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="30">
+        <v>4740</v>
+      </c>
+      <c r="C11" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="17">
-        <v>4740</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>9</v>
+      <c r="D11" s="22" t="s">
+        <v>8</v>
       </c>
       <c r="E11" s="10">
         <v>10718</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="26"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="23"/>
       <c r="E12" s="11">
         <v>11443</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="26"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="23"/>
       <c r="E13" s="10">
         <v>10636</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="26"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="23"/>
       <c r="E14" s="11">
         <v>12675</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="26"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="23"/>
       <c r="E15" s="10">
         <v>11350</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="26"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="23"/>
       <c r="E16" s="11">
         <v>11016</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="26"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="23"/>
       <c r="E17" s="10">
         <v>10894</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="21"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="26"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="23"/>
       <c r="E18" s="11">
         <v>10078</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="21"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="26"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="23"/>
       <c r="E19" s="10">
         <v>10096</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="22"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="27"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="24"/>
       <c r="E20" s="12">
         <v>10861</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="s">
-        <v>38</v>
-      </c>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="D11:D20"/>
     <mergeCell ref="A11:A20"/>
     <mergeCell ref="A5:A9"/>

--- a/data/trees/robustness_analyses.xlsx
+++ b/data/trees/robustness_analyses.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Nature_submission_verified_red/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Nature_submission_0803/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A4ABD2-4982-FC44-A48E-6CDA09DB6616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CE9A22-AE13-A540-BA14-1B85B9B6BDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,9 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="40">
   <si>
-    <t>Extended Data Table 5 | Independent tests of the TACK–Asgard topology</t>
-  </si>
-  <si>
     <t>Robustness analysis</t>
   </si>
   <si>
@@ -140,6 +137,9 @@
   </si>
   <si>
     <t>–</t>
+  </si>
+  <si>
+    <t>Extended Data Table 3 | Independent tests of the TACK–Asgard topology</t>
   </si>
 </sst>
 </file>
@@ -352,58 +352,58 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -587,378 +587,378 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="28" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="C2" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="D2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="G2" s="10" t="s">
         <v>6</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="3">
         <v>4743</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
         <v>10</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>11</v>
       </c>
       <c r="B4" s="5">
         <v>4787</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+      <c r="B5" s="18">
+        <v>4740</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="13">
-        <v>4740</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="24"/>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="11"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="24"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="7" t="s">
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="24"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="6" t="s">
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="25"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="4" t="s">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" s="19" t="s">
-        <v>24</v>
       </c>
       <c r="B10" s="5">
         <v>4740</v>
       </c>
       <c r="C10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="6" t="s">
+      <c r="G10" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+      <c r="B11" s="18">
+        <v>4740</v>
+      </c>
+      <c r="C11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="13">
-        <v>4740</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="12">
+        <v>10718</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="20">
-        <v>10718</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="G11" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="19"/>
+      <c r="E12" s="13">
+        <v>11443</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="22">
-        <v>11443</v>
-      </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="19"/>
+      <c r="E13" s="12">
+        <v>10636</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="20">
-        <v>10636</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="19"/>
+      <c r="E14" s="13">
+        <v>12675</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="22">
-        <v>12675</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="19"/>
+      <c r="E15" s="12">
+        <v>11350</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="20">
-        <v>11350</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="19"/>
+      <c r="E16" s="13">
+        <v>11016</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="35.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="19"/>
+      <c r="E17" s="12">
+        <v>10894</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="22">
-        <v>11016</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="35.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="20">
-        <v>10894</v>
-      </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="19"/>
+      <c r="E18" s="13">
+        <v>10078</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="21"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="22">
-        <v>10078</v>
-      </c>
-      <c r="F18" s="6" t="s">
+      <c r="G18" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="19"/>
+      <c r="E19" s="12">
+        <v>10096</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="21"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="20">
-        <v>10096</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>36</v>
-      </c>
       <c r="G19" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="23"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="24">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="20"/>
+      <c r="E20" s="14">
         <v>10861</v>
       </c>
-      <c r="F20" s="25" t="s">
+      <c r="F20" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="36" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="8">
